--- a/course-design-2/outputs/tables/ch4/32_lifecycle_salary_association.xlsx
+++ b/course-design-2/outputs/tables/ch4/32_lifecycle_salary_association.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_招聘轮次检验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_重招间隔与薪资" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_重招间隔检验" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_方法与口径" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_方法与统计范围" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/course-design-2/outputs/tables/ch4/32_lifecycle_salary_association.xlsx
+++ b/course-design-2/outputs/tables/ch4/32_lifecycle_salary_association.xlsx
@@ -531,9 +531,6 @@
       <c r="G2" t="n">
         <v>90</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>否（样本不足，仅作描述统计）</t>
@@ -544,8 +541,6 @@
           <t>Mann–Whitney U（双侧）+ Cliff's δ</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -741,7 +736,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>分组口径</t>
+          <t>分组设定</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
